--- a/data/transfer_options.xlsx
+++ b/data/transfer_options.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TransferOptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TransferOptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Notes &amp; Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3958,6 +3958,363 @@
       <c r="M60" s="5" t="inlineStr">
         <is>
           <t>Comparable to the Geneva private rate for a similar distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MXP</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cervinia (Breuil-Cervinia)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>70</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>165</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>SkiHolidayTransfers / Alps2Alps</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>EUR70pp winter season via skiholidaytransfers.com; Alps2Alps quotes 'from EUR50pp' as a lower headline figure. 2-3h10 journey depending on source; 165min used to match this resort's existing transfer_minutes_by_airport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MXP</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cervinia (Breuil-Cervinia)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>516</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>165</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SkiHolidayTransfers</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>EUR516 total via skiholidaytransfers.com ('starting from'); vehicle capacity not stated on the source page -- 8 assumed, matching this dataset's standard private-minivan convention elsewhere (e.g. Chamonix, Grandvalira), not a source-confirmed number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BCN</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Grandvalira (Andorra)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>72</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>190</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Alps2Alps / various</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>EUR72pp 'starting from', Barcelona to Pas de la Casa (a Grandvalira sector), ~3h10 journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BCN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Grandvalira (Andorra)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>240</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>180</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Chofix</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>EUR240 for an Opel Vivaro (up to 8 passengers) via chofix.com's published vehicle-tier pricing; taxes/tips included per that page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PDV</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pamporovo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>35</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>90</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Pamporovo Express</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2-person tier from an ARCHIVED 2022-23 winter rate card (pamporovoexpress.com/prices, page itself flags these dates) -- no current-season source found despite a real search effort. Directionally real, not verified current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PDV</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pamporovo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>119</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>90</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Pamporovo Express</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>5-8 person tier from the same archived 2022-23 rate card as the shared_shuttle row above -- same staleness caveat.</t>
         </is>
       </c>
     </row>

--- a/data/transfer_options.xlsx
+++ b/data/transfer_options.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -525,14 +525,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Transfer Options — Geneva (GVA) + Innsbruck (INN) research pass</t>
+          <t>Transfer Options — GVA/INN research pass, extended 2026-08-27 to the 15 resorts that previously had none</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per (airport, resort, mode). 'Cost Basis' is the key field: per_person scales with group size, per_vehicle does not — which is what fixes the group-size flaw in the old distance formula. Yellow = estimated (not individually sourced). Blue = mandatory mode (no alternative exists). Prices are 2026/27 season indications, NOT live quotes — re-verify before booking.</t>
+          <t>Mostly one row per (airport, resort, mode); the 2026-08-27 pass also adds SEPARATE ROWS FOR DIFFERENT VEHICLE CAPACITIES of the same mode, because select_transfer() picks the cheapest per-person option and a 3-seat taxi genuinely beats an 8-seat minibus for a couple (and the reverse for a group of 8). 'Cost Basis' remains the key field: per_person scales with group size, per_vehicle does not. Prices are season indications, NOT live quotes — re-verify before booking. Non-EUR sources are converted at the ECB reference rate for 2026-08-26 (GBP-&gt;EUR 1.168) with the native figure preserved in the note column. 'Round Trip? = Yes' means the price is ALREADY a return fare and must not be doubled.</t>
         </is>
       </c>
     </row>
@@ -4315,6 +4315,1547 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>5-8 person tier from the same archived 2022-23 rate card as the shared_shuttle row above -- same staleness caveat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SOF</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Bansko</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>150</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bansko Express</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>GBP34pp one-way at 2 passengers (banskoexpress.com/prices), converted at ECB 2026-08-26 GBP-&gt;EUR 1.168. NOTE: this operator's per-person rate FALLS with group size (GBP39 @1, GBP34 @2, GBP30 @3, GBP25 @4+); per_person basis can't express that, so this overstates for groups of 4+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SOF</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Bansko</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>170</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68" t="n">
+        <v>150</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Pirin Transfers</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>EUR170 per vehicle up to 8 (pirintransfers.com/bansko-transfer-prices-2026/). Native EUR, no conversion. Corroborated by Bansko Express GBP154 (~EUR180) for the same run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SZG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Saalbach-Hinterglemm</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>40</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>85</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Alps2Alps</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>EUR40pp one-way (alps2alps.com/salzburg-airport/salzburg-to-saalbach-transfer/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>INN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mayrhofen</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>23</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>60</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Alps2Alps</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>EUR23pp one-way (alps2alps.com/innsbruck-airport/innsbruck-to-mayrhofen-transfer/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>INN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Mayrhofen</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>120</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>OeBB bus + OeBB rail + Zillertalbahn</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>sourced_conflicting</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>EUR17.40 composite: airport-&gt;Innsbruck Hbf bus, OeBB to Jenbach, Zillertalbahn to Mayrhofen. Source page (welcomepickups.com) returned 403 to direct fetch -- figure is from the indexed snippet only, NOT independently verified. Jenbach-&gt;Mayrhofen leg alone corroborates ~EUR13 via Trainline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SZG</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Zell am See</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>36</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>75</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Alps2Alps</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>EUR36pp one-way (alps2alps.com/salzburg-airport/salzburg-to-zell-am-see-transfer/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SZG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Zell am See</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>15</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>105</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>OeBB</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>EUR15 Salzburg Hbf-&gt;Zell am See, hourly, direct, ~1h33-1h45 (omio.com). EXCLUDES the SZG airport-&gt;Hbf leg, which is required; duration is the rail leg only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OTP</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Poiana Brasov</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>173</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>150</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bucharest Transfer (Kraken Travel)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>EUR173 all-inclusive private taxi 1-3 pax (bucharesttransfer.com/en/airport-transfer/bucharest-otopeni-airport/poiana-brasov). Chosen over how2transfer.com's 'from EUR140.75 (price per person with 4 passengers)' because that page's own wording is self-contradictory -- the per-person reading implies EUR563/vehicle, far above this operator's 8-seat minibus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>OTP</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Poiana Brasov</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>318</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>150</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bucharest Transfer (Kraken Travel)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>EUR318 all-inclusive private minibus 1-8 pax, same published table as the 1-3 taxi row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LJU</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kranjska Gora</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>110</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Airtrail</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>EUR110 per car up to 4 (airportljubljana.co/Transfer_to_Kranjska_Gora.php).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LJU</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kranjska Gora</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>150</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" t="n">
+        <v>50</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Airtrail</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>EUR150 per minivan up to 8, same published page as the 4-seat row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LJU</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kranjska Gora</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>135</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>GoOpti / Nomago / FlixBus</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>sourced_conflicting</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>EUR10pp from an Omio listing of the real operators' fares, not the operators' own pages (both price dynamically behind a booking form). Slowest option at ~2h15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LJU</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Krvavec</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>39</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>15</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Airtrail</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>EUR39 per car up to 3 (airportljubljana.co/To_ski_resort_Krvavec.php). Confirms Krvavec's proximity selling point: ~15min from LJU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ZAZ</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Formigal</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>25</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>148</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Avanza Aragon</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>sourced_conflicting</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>EUR25pp Zaragoza-&gt;Sallent de Gallego, 4/day, from an Omio listing of Avanza's fare rather than Avanza's own page (which prices behind a booking form).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BCN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Vallnord (Pal-Arinsal)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>195</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Andorra Direct Bus</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>EUR31.50pp, 16 services/day (andorradirectbus.es). TERMINATES ANDORRA LA VELLA, not the resort -- a further local leg is required and is NOT included in this price or duration. The operator's own page also states 'from EUR35' elsewhere; lower published figure used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TRN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Bardonecchia</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>9</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>90</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Trenitalia (Regionale)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>EUR9 advance Regionale fare from Torino Porta Nuova/Porta Susa -- NOT from TRN (Caselle) airport; a ~40min airport-&gt;city leg is required and is not in this price or duration. Still far the best value on this route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TRN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bardonecchia</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>294.44</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" t="n">
+        <v>75</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Suntransfers</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>EUR294.44 per car up to 4 (suntransfers.com/turin-airport-to-bardonecchia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TRN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Bardonecchia</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>75</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Suntransfers</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>EUR343.51 per minivan up to 8, same operator/page as the 4-seat row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BGY</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Passo Tonale</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>292.33</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>125</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Suntransfers</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>EUR292.33 per car up to 4 (suntransfers.com/milan-bergamo-airport-to-passo-del-tonale). Page does not state one-way vs return; recorded as one-way (this operator's standard quote basis). Public transport on this route was verified at 5h41 via Brescia/Edolo -- real but impractical, and no usable EUR fare was published, so it is deliberately not recorded as a row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CMF</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Les Arcs</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>62</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>105</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Alps2Alps</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>EUR62pp as published (alps2alps.com/chambery-airport/...-les-arcs-1950-2000-paradiski-...). Page advertises 'from EUR62 per person' while also listing 3/7/8/12-16 seat vehicle tiers, so the per_person basis is as-published but may really be a per-vehicle product marketed per head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CMF</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Les Arcs</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>267.67</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>105</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Suntransfers</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>EUR267.67 per minivan up to 8 (suntransfers.com/chambery-airport-to-les-arcs-1950-2000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Les Arcs</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>195</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>SA,SU</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Ben's Bus</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>GBP82pp RETURN (bensbus.co.uk) -- already a return fare, must NOT be doubled. Converted at ECB 2026-08-26 GBP-&gt;EUR 1.168. WEEKENDS ONLY, 12 Dec 2026-17 Apr 2027. Ben's Bus publishes no Chambery-&gt;Les Arcs fare at all despite listing that route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Avoriaz</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>30</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>85</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Alps2Alps</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>EUR30pp one-way (alps2alps.com/geneva-airport/geneva-to-avoriaz-transfer/). AVORIAZ IS CAR-FREE: no vehicle reaches the village; shared transfers terminate at the Prodains cable car base (or the Welcome Centre outside cable-car hours) and a further cable-car leg is always required. Not flagged mandatory because, unlike Zermatt, the road transfer does reach the lift base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Avoriaz</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>110</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>AlpyBus</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>EUR69.50pp door-to-door (alpybus.com/avoriaz). The EUR30-vs-EUR69.50 spread against Alps2Alps for a nominally similar service is real and mirrors the GVA-&gt;Verbier spread already in this table: fixed-point vs door-to-door service explains most of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Avoriaz</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>private_transfer</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>270.58</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>per_vehicle</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" t="n">
+        <v>110</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Suntransfers</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>EUR270.58 per minivan up to 8 (suntransfers.com/geneva-airport-to-avoriaz). Anomaly recorded as published: this 8-seat minivan is CHEAPER than the same operator's 4-seat car (EUR351.43).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Les Menuires</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>shared_shuttle</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>per_person</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>180</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SA,SU</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Ben's Bus</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>GBP80pp RETURN (bensbus.co.uk) -- already a return fare, must NOT be doubled. Converted at ECB 2026-08-26 GBP-&gt;EUR 1.168. WEEKENDS ONLY, 5 Dec 2026-24 Apr 2027, 146km/~3h. NOTE: recorded against GVA, not this resort's stored nearest_airport (CMF) -- no operator publishes a CMF-&gt;Les Menuires fare. Interacts with the known transfer-airport-consistency gap.</t>
         </is>
       </c>
     </row>
